--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T10:39:42+00:00</t>
+    <t>2026-07-23T11:20:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T11:20:28+00:00</t>
+    <t>2026-07-23T15:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T15:55:45+00:00</t>
+    <t>2026-07-24T06:29:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T06:29:13+00:00</t>
+    <t>2026-09-03T10:43:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,58 +79,61 @@
     <t>Jurisdiction</t>
   </si>
   <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ValueSet zur Dokumentation von Änderungen bei Symptomen/Phänotypen über Zeit. Kombiniert MVGenomSeq-spezifische Codes mit SNOMED CT-Codes für internationale Interoperabilität.</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Immutable</t>
+  </si>
+  <si>
+    <t>BooleanType[null]</t>
+  </si>
+  <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>newly-added</t>
+  </si>
+  <si>
+    <t>Neu hinzugefügt</t>
+  </si>
+  <si>
+    <t>improved</t>
+  </si>
+  <si>
+    <t>Verbessert</t>
+  </si>
+  <si>
+    <t>degraded</t>
+  </si>
+  <si>
+    <t>Verschlechtert</t>
+  </si>
+  <si>
+    <t>no-longer-observed</t>
+  </si>
+  <si>
+    <t>Nicht mehr beobachtet</t>
+  </si>
+  <si>
+    <t>unchanged</t>
+  </si>
+  <si>
+    <t>Unverändert</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>ValueSet zur Dokumentation von Änderungen bei Symptomen/Phänotypen über Zeit. Kombiniert MVGenomSeq-spezifische Codes mit SNOMED CT-Codes für internationale Interoperabilität.</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Immutable</t>
-  </si>
-  <si>
-    <t>BooleanType[null]</t>
-  </si>
-  <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>newly-added</t>
-  </si>
-  <si>
-    <t>Neu hinzugefügt</t>
-  </si>
-  <si>
-    <t>improved</t>
-  </si>
-  <si>
-    <t>Verbessert</t>
-  </si>
-  <si>
-    <t>degraded</t>
-  </si>
-  <si>
-    <t>Verschlechtert</t>
-  </si>
-  <si>
-    <t>no-longer-observed</t>
-  </si>
-  <si>
-    <t>Nicht mehr beobachtet</t>
-  </si>
-  <si>
-    <t>unchanged</t>
-  </si>
-  <si>
-    <t>Unverändert</t>
   </si>
   <si>
     <t>System URI</t>
@@ -496,18 +499,18 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -534,66 +537,66 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:43:48+00:00</t>
+    <t>2026-09-03T17:01:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T17:01:55+00:00</t>
+    <t>2026-09-04T05:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T05:29:06+00:00</t>
+    <t>2026-09-04T06:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T06:37:14+00:00</t>
+    <t>2026-09-04T07:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T07:02:52+00:00</t>
+    <t>2026-09-04T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T08:01:15+00:00</t>
+    <t>2026-09-04T11:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:35:42+00:00</t>
+    <t>2026-09-04T11:52:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:52:20+00:00</t>
+    <t>2026-09-04T12:44:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T12:44:12+00:00</t>
+    <t>2026-09-04T13:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T13:01:37+00:00</t>
+    <t>2026-09-04T16:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T16:11:50+00:00</t>
+    <t>2026-09-04T16:57:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T16:57:12+00:00</t>
+    <t>2026-09-07T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T15:50:41+00:00</t>
+    <t>2026-09-07T16:06:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T16:06:13+00:00</t>
+    <t>2026-09-08T09:14:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:14:37+00:00</t>
+    <t>2026-09-08T09:32:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:32:56+00:00</t>
+    <t>2026-09-08T15:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T15:03:47+00:00</t>
+    <t>2026-09-09T09:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T09:29:55+00:00</t>
+    <t>2026-09-09T10:02:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:02:49+00:00</t>
+    <t>2026-09-09T11:08:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:08:17+00:00</t>
+    <t>2026-09-09T11:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:49:20+00:00</t>
+    <t>2026-09-11T10:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T10:52:45+00:00</t>
+    <t>2026-09-11T12:45:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
+++ b/branches/dev/ValueSet-mii-vs-seltene-symptom-change-status-combined.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:45:52+00:00</t>
+    <t>2026-09-11T14:10:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
